--- a/assets/master-template.xlsx
+++ b/assets/master-template.xlsx
@@ -21403,13 +21403,18 @@
     </row>
     <row r="4" spans="1:25" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="A4" s="598"/>
-      <c r="B4" s="39"/>
+      <c r="B4" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Total shares outstanding (leave blank to use the direct-holder total)</t>
+        </is>
+      </c>
       <c r="C4" s="39"/>
       <c r="D4" s="39"/>
       <c r="E4" s="39"/>
       <c r="F4" s="371"/>
       <c r="G4" s="372"/>
       <c r="H4" s="371"/>
+      <c r="J4" s="371"/>
     </row>
     <row r="5" spans="1:25" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="670" t="s">
@@ -21490,13 +21495,11 @@
       </c>
       <c r="K7" s="378"/>
       <c r="L7" s="407">
-        <f>IFERROR(H7/$H$27,0)</f>
-        <v>1</v>
+        <f>IFERROR(H7/IF($H$4&gt;0,$H$4,$H$27),0)</f>
       </c>
       <c r="M7" s="378"/>
       <c r="N7" s="410">
-        <f>IFERROR(J7/$J$27,0)</f>
-        <v>0.6</v>
+        <f>IFERROR(J7/IF($J$4&gt;0,$J$4,$J$27),0)</f>
       </c>
       <c r="P7" s="604"/>
     </row>
@@ -21515,13 +21518,11 @@
       <c r="J8" s="601"/>
       <c r="K8" s="378"/>
       <c r="L8" s="408">
-        <f t="shared" ref="L8:L14" si="0">IFERROR(H8/$H$27,0)</f>
-        <v>0</v>
+        <f t="shared" ref="L8:L14" si="0">IFERROR(H8/IF($H$4&gt;0,$H$4,$H$27),0)</f>
       </c>
       <c r="M8" s="378"/>
       <c r="N8" s="411">
-        <f t="shared" ref="N8:N14" si="1">IFERROR(J8/$J$27,0)</f>
-        <v>0</v>
+        <f t="shared" ref="N8:N14" si="1">IFERROR(J8/IF($J$4&gt;0,$J$4,$J$27),0)</f>
       </c>
       <c r="P8" s="605"/>
     </row>
@@ -21808,13 +21809,11 @@
       </c>
       <c r="K19" s="378"/>
       <c r="L19" s="407">
-        <f t="shared" ref="L19:L26" si="2">IFERROR(H19/$H$27,0)</f>
-        <v>1</v>
+        <f t="shared" ref="L19:L26" si="2">IFERROR(H19/IF($H$4&gt;0,$H$4,$H$27),0)</f>
       </c>
       <c r="M19" s="378"/>
       <c r="N19" s="410">
-        <f>IFERROR(J19/$J$27,0)</f>
-        <v>0.6</v>
+        <f>IFERROR(J19/IF($J$4&gt;0,$J$4,$J$27),0)</f>
       </c>
       <c r="O19" s="39"/>
       <c r="P19" s="39"/>
@@ -21852,8 +21851,7 @@
       </c>
       <c r="M20" s="378"/>
       <c r="N20" s="411">
-        <f t="shared" ref="N20:N26" si="3">IFERROR(J20/$J$27,0)</f>
-        <v>0.2</v>
+        <f t="shared" ref="N20:N26" si="3">IFERROR(J20/IF($J$4&gt;0,$J$4,$J$27),0)</f>
       </c>
       <c r="O20" s="39"/>
       <c r="P20" s="39"/>

--- a/assets/master-template.xlsx
+++ b/assets/master-template.xlsx
@@ -17178,7 +17178,7 @@
       </c>
       <c r="C82" s="437"/>
       <c r="D82" s="347" t="e">
-        <f>F81*'Shareholding Details'!N19</f>
+        <f>F81*'Shareholding Details'!N16</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -17474,7 +17474,7 @@
       <c r="D16" s="370"/>
       <c r="E16" s="370"/>
       <c r="F16" s="420">
-        <f>F15*'Shareholding Details'!N19</f>
+        <f>F15*'Shareholding Details'!N16</f>
         <v>0</v>
       </c>
     </row>
@@ -17630,7 +17630,7 @@
       <c r="C27" s="370"/>
       <c r="D27" s="370"/>
       <c r="F27" s="420">
-        <f>F26*'Shareholding Details'!N19</f>
+        <f>F26*'Shareholding Details'!N16</f>
         <v>0</v>
       </c>
     </row>
@@ -17818,7 +17818,7 @@
       </c>
       <c r="E7" s="372"/>
       <c r="F7" s="490">
-        <f>'Shareholding Details'!N19</f>
+        <f>'Shareholding Details'!N16</f>
         <v>0.6</v>
       </c>
     </row>
@@ -22846,7 +22846,7 @@
     <tabColor theme="3" tint="-0.249977111117893"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P64"/>
+  <dimension ref="A1:P72"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.453125" customWidth="1"/>
@@ -23665,22 +23665,22 @@
         <v>17</v>
       </c>
       <c r="F33" s="65">
-        <f>SUM(F34:F50)</f>
+        <f>SUM(F34:F58)</f>
         <v>0</v>
       </c>
       <c r="G33" s="66"/>
       <c r="H33" s="65">
-        <f>SUM(H34:H50)</f>
+        <f>SUM(H34:H58)</f>
         <v>0</v>
       </c>
       <c r="I33" s="66"/>
       <c r="J33" s="65">
-        <f>SUM(J34:J50)</f>
+        <f>SUM(J34:J58)</f>
         <v>0</v>
       </c>
       <c r="K33" s="66"/>
       <c r="L33" s="103" t="e">
-        <f>SUM(L34:L50)</f>
+        <f>SUM(L34:L58)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -23697,12 +23697,12 @@
       <c r="H34" s="621"/>
       <c r="I34" s="100"/>
       <c r="J34" s="100">
-        <f t="shared" ref="J34:J50" si="6">H34+F34</f>
+        <f t="shared" ref="J34:J58" si="6">H34+F34</f>
         <v>0</v>
       </c>
       <c r="K34" s="37"/>
       <c r="L34" s="102" t="e">
-        <f t="shared" ref="L34:L50" si="7">J34/$L$5</f>
+        <f t="shared" ref="L34:L58" si="7">J34/$L$5</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -24058,346 +24058,534 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="51" spans="1:16" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="678"/>
-      <c r="B51" s="79">
-        <v>18</v>
-      </c>
-      <c r="C51" s="80" t="s">
-        <v>121</v>
-      </c>
-      <c r="D51" s="81"/>
-      <c r="E51" s="82">
-        <v>18</v>
-      </c>
-      <c r="F51" s="83">
-        <f>SUM(F26:F33)</f>
-        <v>0</v>
-      </c>
-      <c r="G51" s="84"/>
-      <c r="H51" s="83">
-        <f>SUM(H26:H33)</f>
-        <v>0</v>
-      </c>
-      <c r="I51" s="84"/>
-      <c r="J51" s="83">
-        <f>SUM(J26:J33)</f>
-        <v>0</v>
-      </c>
-      <c r="K51" s="84"/>
-      <c r="L51" s="85" t="e">
-        <f>SUM(L26:L33)</f>
+    <row r="51" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A51" s="677"/>
+      <c r="B51" s="53"/>
+      <c r="C51" s="99" t="inlineStr">
+        <is>
+          <t>Other deduction 18</t>
+        </is>
+      </c>
+      <c r="D51" s="54"/>
+      <c r="E51" s="60"/>
+      <c r="F51" s="621"/>
+      <c r="G51" s="100"/>
+      <c r="H51" s="621"/>
+      <c r="I51" s="100"/>
+      <c r="J51" s="100">
+        <f>H51+F51</f>
+        <v>0</v>
+      </c>
+      <c r="K51" s="100"/>
+      <c r="L51" s="102" t="e">
+        <f>J51/$L$5</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="52" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A52" s="677" t="s">
-        <v>122</v>
-      </c>
-      <c r="B52" s="106">
-        <v>19</v>
-      </c>
-      <c r="C52" s="107" t="s">
-        <v>123</v>
-      </c>
-      <c r="D52" s="108"/>
-      <c r="E52" s="109">
-        <v>19</v>
-      </c>
-      <c r="F52" s="112">
-        <f>F25-F51</f>
-        <v>0</v>
-      </c>
-      <c r="G52" s="110"/>
-      <c r="H52" s="112">
-        <f>H25-H51</f>
-        <v>0</v>
-      </c>
-      <c r="I52" s="110"/>
-      <c r="J52" s="112">
-        <f>J25-J51</f>
-        <v>0</v>
-      </c>
-      <c r="K52" s="110"/>
-      <c r="L52" s="111" t="e">
-        <f>L25-L51</f>
+      <c r="A52" s="677"/>
+      <c r="B52" s="53"/>
+      <c r="C52" s="99" t="inlineStr">
+        <is>
+          <t>Other deduction 19</t>
+        </is>
+      </c>
+      <c r="D52" s="54"/>
+      <c r="E52" s="60"/>
+      <c r="F52" s="621"/>
+      <c r="G52" s="100"/>
+      <c r="H52" s="621"/>
+      <c r="I52" s="100"/>
+      <c r="J52" s="100">
+        <f>H52+F52</f>
+        <v>0</v>
+      </c>
+      <c r="K52" s="100"/>
+      <c r="L52" s="102" t="e">
+        <f>J52/$L$5</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="53" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A53" s="677"/>
-      <c r="B53" s="53">
-        <v>20</v>
-      </c>
-      <c r="C53" s="68" t="s">
-        <v>124</v>
+      <c r="B53" s="53"/>
+      <c r="C53" s="99" t="inlineStr">
+        <is>
+          <t>Other deduction 20</t>
+        </is>
       </c>
       <c r="D53" s="54"/>
-      <c r="E53" s="60">
-        <v>20</v>
-      </c>
-      <c r="F53" s="619"/>
-      <c r="G53" s="56"/>
-      <c r="H53" s="620"/>
-      <c r="I53" s="56"/>
-      <c r="J53" s="57">
-        <f t="shared" ref="J53:J55" si="8">H53+F53</f>
-        <v>0</v>
-      </c>
-      <c r="K53" s="56"/>
-      <c r="L53" s="59" t="e">
+      <c r="E53" s="60"/>
+      <c r="F53" s="621"/>
+      <c r="G53" s="100"/>
+      <c r="H53" s="621"/>
+      <c r="I53" s="100"/>
+      <c r="J53" s="100">
+        <f>H53+F53</f>
+        <v>0</v>
+      </c>
+      <c r="K53" s="100"/>
+      <c r="L53" s="102" t="e">
         <f>J53/$L$5</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N53" t="s">
-        <v>125</v>
-      </c>
-      <c r="P53" s="549" t="e">
-        <f>-J54/J52</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A54" s="677"/>
-      <c r="B54" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="C54" s="68" t="s">
-        <v>127</v>
-      </c>
-      <c r="D54" s="69"/>
-      <c r="E54" s="60" t="s">
-        <v>126</v>
-      </c>
-      <c r="F54" s="620"/>
-      <c r="G54" s="56"/>
-      <c r="H54" s="620"/>
-      <c r="I54" s="56"/>
-      <c r="J54" s="57">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K54" s="56"/>
-      <c r="L54" s="59" t="e">
+      <c r="B54" s="53"/>
+      <c r="C54" s="99" t="inlineStr">
+        <is>
+          <t>Other deduction 21</t>
+        </is>
+      </c>
+      <c r="D54" s="54"/>
+      <c r="E54" s="60"/>
+      <c r="F54" s="621"/>
+      <c r="G54" s="100"/>
+      <c r="H54" s="621"/>
+      <c r="I54" s="100"/>
+      <c r="J54" s="100">
+        <f>H54+F54</f>
+        <v>0</v>
+      </c>
+      <c r="K54" s="100"/>
+      <c r="L54" s="102" t="e">
         <f>J54/$L$5</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A55" s="677"/>
-      <c r="B55" s="53" t="s">
-        <v>89</v>
-      </c>
-      <c r="C55" s="68" t="s">
-        <v>128</v>
-      </c>
-      <c r="D55" s="69"/>
-      <c r="E55" s="60" t="s">
-        <v>89</v>
-      </c>
-      <c r="F55" s="620"/>
-      <c r="G55" s="56"/>
-      <c r="H55" s="620"/>
-      <c r="I55" s="56"/>
-      <c r="J55" s="57">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K55" s="56"/>
-      <c r="L55" s="59" t="e">
+      <c r="B55" s="53"/>
+      <c r="C55" s="99" t="inlineStr">
+        <is>
+          <t>Other deduction 22</t>
+        </is>
+      </c>
+      <c r="D55" s="54"/>
+      <c r="E55" s="60"/>
+      <c r="F55" s="621"/>
+      <c r="G55" s="100"/>
+      <c r="H55" s="621"/>
+      <c r="I55" s="100"/>
+      <c r="J55" s="100">
+        <f>H55+F55</f>
+        <v>0</v>
+      </c>
+      <c r="K55" s="100"/>
+      <c r="L55" s="102" t="e">
         <f>J55/$L$5</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="56" spans="1:16" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="678"/>
-      <c r="B56" s="79">
-        <v>22</v>
-      </c>
-      <c r="C56" s="80" t="s">
-        <v>129</v>
-      </c>
-      <c r="D56" s="81"/>
-      <c r="E56" s="82">
-        <v>22</v>
-      </c>
-      <c r="F56" s="83">
-        <f>SUM(F52:F55)</f>
-        <v>0</v>
-      </c>
-      <c r="G56" s="84"/>
-      <c r="H56" s="83">
-        <f>SUM(H52:H55)</f>
-        <v>0</v>
-      </c>
-      <c r="I56" s="84"/>
-      <c r="J56" s="83">
-        <f>SUM(J52:J55)</f>
-        <v>0</v>
-      </c>
-      <c r="K56" s="84"/>
-      <c r="L56" s="85" t="e">
-        <f>SUM(L52:L55)</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="57" spans="1:16" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="677" t="s">
-        <v>130</v>
-      </c>
-      <c r="B57" s="53" t="s">
-        <v>131</v>
-      </c>
-      <c r="C57" s="80" t="s">
-        <v>129</v>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A56" s="677"/>
+      <c r="B56" s="53"/>
+      <c r="C56" s="99" t="inlineStr">
+        <is>
+          <t>Other deduction 23</t>
+        </is>
+      </c>
+      <c r="D56" s="54"/>
+      <c r="E56" s="60"/>
+      <c r="F56" s="621"/>
+      <c r="G56" s="100"/>
+      <c r="H56" s="621"/>
+      <c r="I56" s="100"/>
+      <c r="J56" s="100">
+        <f>H56+F56</f>
+        <v>0</v>
+      </c>
+      <c r="K56" s="100"/>
+      <c r="L56" s="102" t="e">
+        <f>J56/$L$5</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A57" s="677"/>
+      <c r="B57" s="53"/>
+      <c r="C57" s="99" t="inlineStr">
+        <is>
+          <t>Other deduction 24</t>
+        </is>
       </c>
       <c r="D57" s="54"/>
-      <c r="E57" s="60" t="s">
-        <v>131</v>
-      </c>
-      <c r="F57" s="619"/>
-      <c r="G57" s="56"/>
-      <c r="H57" s="620"/>
-      <c r="I57" s="56"/>
-      <c r="J57" s="57">
-        <f t="shared" ref="J57" si="9">H57+F57</f>
-        <v>0</v>
-      </c>
-      <c r="K57" s="56"/>
-      <c r="L57" s="59" t="e">
+      <c r="E57" s="60"/>
+      <c r="F57" s="621"/>
+      <c r="G57" s="100"/>
+      <c r="H57" s="621"/>
+      <c r="I57" s="100"/>
+      <c r="J57" s="100">
+        <f>H57+F57</f>
+        <v>0</v>
+      </c>
+      <c r="K57" s="100"/>
+      <c r="L57" s="102" t="e">
         <f>J57/$L$5</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A58" s="677"/>
-      <c r="B58" s="53" t="s">
+      <c r="B58" s="53"/>
+      <c r="C58" s="99" t="inlineStr">
+        <is>
+          <t>Other deduction 25</t>
+        </is>
+      </c>
+      <c r="D58" s="54"/>
+      <c r="E58" s="60"/>
+      <c r="F58" s="621"/>
+      <c r="G58" s="100"/>
+      <c r="H58" s="621"/>
+      <c r="I58" s="100"/>
+      <c r="J58" s="100">
+        <f>H58+F58</f>
+        <v>0</v>
+      </c>
+      <c r="K58" s="100"/>
+      <c r="L58" s="102" t="e">
+        <f>J58/$L$5</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A59" s="678"/>
+      <c r="B59" s="79">
+        <v>18</v>
+      </c>
+      <c r="C59" s="80" t="s">
+        <v>121</v>
+      </c>
+      <c r="D59" s="81"/>
+      <c r="E59" s="82">
+        <v>18</v>
+      </c>
+      <c r="F59" s="83">
+        <f>SUM(F26:F33)</f>
+        <v>0</v>
+      </c>
+      <c r="G59" s="84"/>
+      <c r="H59" s="83">
+        <f>SUM(H26:H33)</f>
+        <v>0</v>
+      </c>
+      <c r="I59" s="84"/>
+      <c r="J59" s="83">
+        <f>SUM(J26:J33)</f>
+        <v>0</v>
+      </c>
+      <c r="K59" s="84"/>
+      <c r="L59" s="85" t="e">
+        <f>SUM(L26:L33)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A60" s="677" t="s">
+        <v>122</v>
+      </c>
+      <c r="B60" s="106">
+        <v>19</v>
+      </c>
+      <c r="C60" s="107" t="s">
+        <v>123</v>
+      </c>
+      <c r="D60" s="108"/>
+      <c r="E60" s="109">
+        <v>19</v>
+      </c>
+      <c r="F60" s="112">
+        <f>F25-F59</f>
+        <v>0</v>
+      </c>
+      <c r="G60" s="110"/>
+      <c r="H60" s="112">
+        <f>H25-H59</f>
+        <v>0</v>
+      </c>
+      <c r="I60" s="110"/>
+      <c r="J60" s="112">
+        <f>J25-J59</f>
+        <v>0</v>
+      </c>
+      <c r="K60" s="110"/>
+      <c r="L60" s="111" t="e">
+        <f>L25-L59</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A61" s="677"/>
+      <c r="B61" s="53">
+        <v>20</v>
+      </c>
+      <c r="C61" s="68" t="s">
+        <v>124</v>
+      </c>
+      <c r="D61" s="54"/>
+      <c r="E61" s="60">
+        <v>20</v>
+      </c>
+      <c r="F61" s="619"/>
+      <c r="G61" s="56"/>
+      <c r="H61" s="620"/>
+      <c r="I61" s="56"/>
+      <c r="J61" s="57">
+        <f t="shared" ref="J61:J63" si="8">H61+F61</f>
+        <v>0</v>
+      </c>
+      <c r="K61" s="56"/>
+      <c r="L61" s="59" t="e">
+        <f>J61/$L$5</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N61" t="s">
+        <v>125</v>
+      </c>
+      <c r="P61" s="549" t="e">
+        <f>-J62/J60</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A62" s="677"/>
+      <c r="B62" s="53" t="s">
+        <v>126</v>
+      </c>
+      <c r="C62" s="68" t="s">
+        <v>127</v>
+      </c>
+      <c r="D62" s="69"/>
+      <c r="E62" s="60" t="s">
+        <v>126</v>
+      </c>
+      <c r="F62" s="620"/>
+      <c r="G62" s="56"/>
+      <c r="H62" s="620"/>
+      <c r="I62" s="56"/>
+      <c r="J62" s="57">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K62" s="56"/>
+      <c r="L62" s="59" t="e">
+        <f>J62/$L$5</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A63" s="677"/>
+      <c r="B63" s="53" t="s">
         <v>89</v>
       </c>
-      <c r="C58" s="68" t="s">
+      <c r="C63" s="68" t="s">
+        <v>128</v>
+      </c>
+      <c r="D63" s="69"/>
+      <c r="E63" s="60" t="s">
+        <v>89</v>
+      </c>
+      <c r="F63" s="620"/>
+      <c r="G63" s="56"/>
+      <c r="H63" s="620"/>
+      <c r="I63" s="56"/>
+      <c r="J63" s="57">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K63" s="56"/>
+      <c r="L63" s="59" t="e">
+        <f>J63/$L$5</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="64" spans="1:16" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A64" s="678"/>
+      <c r="B64" s="79">
+        <v>22</v>
+      </c>
+      <c r="C64" s="80" t="s">
+        <v>129</v>
+      </c>
+      <c r="D64" s="81"/>
+      <c r="E64" s="82">
+        <v>22</v>
+      </c>
+      <c r="F64" s="83">
+        <f>F60-F62-F63</f>
+      </c>
+      <c r="G64" s="84"/>
+      <c r="H64" s="83">
+        <f>H60-H62-H63</f>
+      </c>
+      <c r="I64" s="84"/>
+      <c r="J64" s="83">
+        <f>J60-J62-J63</f>
+      </c>
+      <c r="K64" s="84"/>
+      <c r="L64" s="85">
+        <f>L60-L62-L63</f>
+      </c>
+    </row>
+    <row r="65" spans="1:16" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A65" s="677" t="s">
+        <v>130</v>
+      </c>
+      <c r="B65" s="53" t="s">
+        <v>131</v>
+      </c>
+      <c r="C65" s="80" t="s">
+        <v>129</v>
+      </c>
+      <c r="D65" s="54"/>
+      <c r="E65" s="60" t="s">
+        <v>131</v>
+      </c>
+      <c r="F65" s="619"/>
+      <c r="G65" s="56"/>
+      <c r="H65" s="620"/>
+      <c r="I65" s="56"/>
+      <c r="J65" s="57">
+        <f t="shared" ref="J65" si="9">H65+F65</f>
+        <v>0</v>
+      </c>
+      <c r="K65" s="56"/>
+      <c r="L65" s="59" t="e">
+        <f>J65/$L$5</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A66" s="677"/>
+      <c r="B66" s="53" t="s">
+        <v>89</v>
+      </c>
+      <c r="C66" s="68" t="s">
         <v>132</v>
       </c>
-      <c r="D58" s="54"/>
-      <c r="E58" s="60" t="s">
+      <c r="D66" s="54"/>
+      <c r="E66" s="60" t="s">
         <v>89</v>
       </c>
-      <c r="F58" s="619"/>
-      <c r="G58" s="56"/>
-      <c r="H58" s="620"/>
-      <c r="I58" s="56"/>
-      <c r="J58" s="57">
-        <f t="shared" ref="J58:J59" si="10">H58+F58</f>
-        <v>0</v>
-      </c>
-      <c r="K58" s="56"/>
-      <c r="L58" s="59" t="e">
-        <f>J58/$L$5</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A59" s="677"/>
-      <c r="B59" s="53" t="s">
+      <c r="F66" s="619"/>
+      <c r="G66" s="56"/>
+      <c r="H66" s="620"/>
+      <c r="I66" s="56"/>
+      <c r="J66" s="57">
+        <f t="shared" ref="J66:J67" si="10">H66+F66</f>
+        <v>0</v>
+      </c>
+      <c r="K66" s="56"/>
+      <c r="L66" s="59" t="e">
+        <f>J66/$L$5</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A67" s="677"/>
+      <c r="B67" s="53" t="s">
         <v>133</v>
       </c>
-      <c r="C59" s="68" t="s">
+      <c r="C67" s="68" t="s">
         <v>134</v>
       </c>
-      <c r="D59" s="69"/>
-      <c r="E59" s="60" t="s">
+      <c r="D67" s="69"/>
+      <c r="E67" s="60" t="s">
         <v>133</v>
       </c>
-      <c r="F59" s="620"/>
-      <c r="G59" s="56"/>
-      <c r="H59" s="620"/>
-      <c r="I59" s="56"/>
-      <c r="J59" s="57">
+      <c r="F67" s="620"/>
+      <c r="G67" s="56"/>
+      <c r="H67" s="620"/>
+      <c r="I67" s="56"/>
+      <c r="J67" s="57">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="K59" s="56"/>
-      <c r="L59" s="59" t="e">
-        <f>J59/$L$5</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="60" spans="1:16" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="678"/>
-      <c r="B60" s="79">
+      <c r="K67" s="56"/>
+      <c r="L67" s="59" t="e">
+        <f>J67/$L$5</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="68" spans="1:16" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A68" s="678"/>
+      <c r="B68" s="79">
         <v>24</v>
       </c>
-      <c r="C60" s="80" t="s">
+      <c r="C68" s="80" t="s">
         <v>135</v>
       </c>
-      <c r="D60" s="81"/>
-      <c r="E60" s="82">
+      <c r="D68" s="81"/>
+      <c r="E68" s="82">
         <v>24</v>
       </c>
-      <c r="F60" s="83">
-        <f>F57+F58-F59</f>
-        <v>0</v>
-      </c>
-      <c r="G60" s="84"/>
-      <c r="H60" s="83">
-        <f>H57+H58-H59</f>
-        <v>0</v>
-      </c>
-      <c r="I60" s="84"/>
-      <c r="J60" s="83">
-        <f>J57+J58-J59</f>
-        <v>0</v>
-      </c>
-      <c r="K60" s="84"/>
-      <c r="L60" s="85" t="e">
-        <f>L57+L58-L59</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M60" s="43"/>
-    </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A61" s="94"/>
-      <c r="B61" s="95"/>
-      <c r="C61" s="96"/>
-      <c r="D61" s="88"/>
-      <c r="E61" s="95"/>
-      <c r="F61" s="97"/>
-      <c r="G61" s="95"/>
-      <c r="H61" s="97"/>
-      <c r="I61" s="95"/>
-      <c r="J61" s="97"/>
-      <c r="K61" s="95"/>
-      <c r="L61" s="97"/>
-    </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A62" s="86"/>
-      <c r="B62" s="56"/>
-      <c r="C62" s="87"/>
-      <c r="D62" s="88"/>
-      <c r="E62" s="56"/>
-      <c r="F62" s="78"/>
-      <c r="G62" s="56"/>
-      <c r="H62" s="78"/>
-      <c r="I62" s="56"/>
-      <c r="J62" s="78"/>
-      <c r="K62" s="56"/>
-      <c r="L62" s="78"/>
-    </row>
-    <row r="63" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B63"/>
-      <c r="C63"/>
-      <c r="D63" s="21"/>
-      <c r="H63"/>
-    </row>
-    <row r="64" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B64"/>
-      <c r="C64"/>
-      <c r="D64" s="21"/>
-      <c r="H64"/>
+      <c r="F68" s="83">
+        <f>F65+F66-F67</f>
+        <v>0</v>
+      </c>
+      <c r="G68" s="84"/>
+      <c r="H68" s="83">
+        <f>H65+H66-H67</f>
+        <v>0</v>
+      </c>
+      <c r="I68" s="84"/>
+      <c r="J68" s="83">
+        <f>J65+J66-J67</f>
+        <v>0</v>
+      </c>
+      <c r="K68" s="84"/>
+      <c r="L68" s="85" t="e">
+        <f>L65+L66-L67</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M68" s="43"/>
+    </row>
+    <row r="69" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A69" s="94"/>
+      <c r="B69" s="95"/>
+      <c r="C69" s="96"/>
+      <c r="D69" s="88"/>
+      <c r="E69" s="95"/>
+      <c r="F69" s="97"/>
+      <c r="G69" s="95"/>
+      <c r="H69" s="97"/>
+      <c r="I69" s="95"/>
+      <c r="J69" s="97"/>
+      <c r="K69" s="95"/>
+      <c r="L69" s="97"/>
+    </row>
+    <row r="70" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A70" s="86"/>
+      <c r="B70" s="56"/>
+      <c r="C70" s="87"/>
+      <c r="D70" s="88"/>
+      <c r="E70" s="56"/>
+      <c r="F70" s="78"/>
+      <c r="G70" s="56"/>
+      <c r="H70" s="78"/>
+      <c r="I70" s="56"/>
+      <c r="J70" s="78"/>
+      <c r="K70" s="56"/>
+      <c r="L70" s="78"/>
+    </row>
+    <row r="71" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="B71"/>
+      <c r="C71"/>
+      <c r="D71" s="21"/>
+      <c r="H71"/>
+    </row>
+    <row r="72" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="B72"/>
+      <c r="C72"/>
+      <c r="D72" s="21"/>
+      <c r="H72"/>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A52:A56"/>
-    <mergeCell ref="A57:A60"/>
+    <mergeCell ref="A60:A64"/>
+    <mergeCell ref="A65:A68"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="A3:L3"/>
@@ -27690,18 +27878,24 @@
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" s="204"/>
-      <c r="B64" s="68"/>
+      <c r="B64" s="68" t="inlineStr">
+        <is>
+          <t>Out of balance (assets less liabilities and capital) — must be nil in every column before filing</t>
+        </is>
+      </c>
       <c r="C64" s="68"/>
-      <c r="D64" s="258"/>
+      <c r="D64" s="258">
+        <f>ROUND(D63-D42,2)</f>
+      </c>
       <c r="E64" s="259"/>
-      <c r="F64" s="260"/>
-      <c r="G64" s="261" t="e">
-        <f>+G63-G42</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H64" s="261" t="e">
-        <f>+H63-H42</f>
-        <v>#DIV/0!</v>
+      <c r="F64" s="260">
+        <f>ROUND(F63-F42,2)</f>
+      </c>
+      <c r="G64" s="261">
+        <f>ROUND(G63-G42,0)</f>
+      </c>
+      <c r="H64" s="261">
+        <f>ROUND(H63-H42,0)</f>
       </c>
       <c r="I64" s="39"/>
     </row>
@@ -28322,11 +28516,17 @@
       <c r="J16" s="2"/>
       <c r="K16" s="638"/>
       <c r="L16" s="2"/>
-      <c r="M16" s="638"/>
+      <c r="M16" s="638">
+        <f>'Income Statement'!J60</f>
+      </c>
       <c r="N16" s="2"/>
-      <c r="O16" s="638"/>
+      <c r="O16" s="638">
+        <f>'Income Statement'!J62</f>
+      </c>
       <c r="P16" s="2"/>
-      <c r="Q16" s="638"/>
+      <c r="Q16" s="638">
+        <f>'Basic Information'!C59</f>
+      </c>
       <c r="R16" s="2"/>
       <c r="S16" s="299">
         <f>ROUND(IFERROR(O16/Q16,0),0)</f>
@@ -30721,7 +30921,7 @@
         <v>1</v>
       </c>
       <c r="I10" s="173">
-        <f>+'Income Statement'!J56</f>
+        <f>+'Income Statement'!J64</f>
         <v>0</v>
       </c>
     </row>
@@ -31554,7 +31754,7 @@
       </c>
       <c r="C43" s="438"/>
       <c r="D43" s="299">
-        <f>'Income Statement'!J51</f>
+        <f>'Income Statement'!J59</f>
         <v>0</v>
       </c>
       <c r="E43" s="387"/>
@@ -31877,6 +32077,9 @@
           <t>Prior 5471</t>
         </is>
       </c>
+      <c r="F10">
+        <f>'Balance Sheet'!D61</f>
+      </c>
       <c r="H10">
         <f>IF(F10="","",ROUND(F10/$F$6,0))</f>
       </c>
@@ -31893,7 +32096,7 @@
         </is>
       </c>
       <c r="F13">
-        <f>'Income Statement'!F56</f>
+        <f>'Income Statement'!F64</f>
       </c>
       <c r="H13">
         <f>ROUND(F13/$J$6,0)</f>
@@ -31971,11 +32174,11 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Translation / other adjustment (confirm — see the re-rollforward exception)</t>
+          <t>Currency translation adjustment (computed: opening balance, income and closing balance translate at three different rates)</t>
         </is>
       </c>
       <c r="H24">
-        <f>IF(F24="","",ROUND(F24/$H$6,0))</f>
+        <f>IF(OR(H28="",H10=""),"",H28-(H10+H13+N(H16)+N(H17)-N(H20)-N(H21)+N(H25)))</f>
       </c>
     </row>
     <row r="25">
@@ -32001,7 +32204,7 @@
         <f>F10+F13+F16+F17-F20-F21+F24+F25</f>
       </c>
       <c r="H27">
-        <f>H10+H13+H16+H17-H20-H21+H24+H25</f>
+        <f>IF(H10="","",H10+H13+N(H16)+N(H17)-N(H20)-N(H21)+N(H25)+N(H24))</f>
       </c>
     </row>
     <row r="28">
@@ -32027,7 +32230,7 @@
         <f>ROUND(F27-F28,2)</f>
       </c>
       <c r="H29">
-        <f>ROUND(H27-H28,0)</f>
+        <f>IF(OR(H27="",H28=""),"",ROUND(H27-H28,0))</f>
       </c>
     </row>
     <row r="31">

--- a/assets/master-template.xlsx
+++ b/assets/master-template.xlsx
@@ -21138,8 +21138,7 @@
         <v>468</v>
       </c>
       <c r="C35" s="473" t="e">
-        <f>ROUND(F38/H38,0)</f>
-        <v>#DIV/0!</v>
+        <f>IFERROR(ROUND(F38/H38,0),"")</f>
       </c>
       <c r="I35">
         <f t="shared" si="0"/>
@@ -21154,8 +21153,7 @@
         <v>469</v>
       </c>
       <c r="C36" s="473" t="e">
-        <f>ROUND(F39/H39,0)</f>
-        <v>#DIV/0!</v>
+        <f>IFERROR(ROUND(F39/H39,0),"")</f>
       </c>
       <c r="I36">
         <f t="shared" si="0"/>
@@ -21170,8 +21168,7 @@
         <v>470</v>
       </c>
       <c r="C37" s="473" t="e">
-        <f>ROUND(F40/H40,0)</f>
-        <v>#DIV/0!</v>
+        <f>IFERROR(ROUND(F40/H40,0),"")</f>
       </c>
       <c r="I37">
         <f t="shared" si="0"/>
@@ -21186,8 +21183,7 @@
         <v>471</v>
       </c>
       <c r="C38" s="473" t="e">
-        <f>ROUND(F41/H41,0)</f>
-        <v>#DIV/0!</v>
+        <f>IFERROR(ROUND(F41/H41,0),"")</f>
       </c>
       <c r="I38">
         <f t="shared" si="0"/>
@@ -21228,8 +21224,7 @@
         <v>474</v>
       </c>
       <c r="C41" s="473" t="e">
-        <f>ROUND(F44/H44,0)</f>
-        <v>#DIV/0!</v>
+        <f>IFERROR(ROUND(F44/H44,0),"")</f>
       </c>
       <c r="I41">
         <f t="shared" si="0"/>
@@ -21270,8 +21265,7 @@
         <v>477</v>
       </c>
       <c r="C44" s="491" t="e">
-        <f>ROUND(F47/H47,0)</f>
-        <v>#DIV/0!</v>
+        <f>IFERROR(ROUND(F47/H47,0),"")</f>
       </c>
       <c r="I44">
         <f t="shared" si="0"/>
